--- a/docs/sample-laporan-OPS-001.xlsx
+++ b/docs/sample-laporan-OPS-001.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="Laporan" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Laporan'!$A1:$S31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Laporan'!$A1:$S37</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="126">
   <si>
     <t>LAPORAN HARIAN PENANGANAN GANGGUAN</t>
   </si>
@@ -199,54 +199,7 @@
     <t>Bringin</t>
   </si>
   <si>
-    <t xml:space="preserve">08:20
-09:05
-10:30
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Cek koneksi ATM, ATM offline.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Koordinasi dengan PLN area, listrik padam.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Listrik kembali normal, ATM online.</t>
-    </r>
+    <t>Cek koneksi ATM, ATM offline.</t>
   </si>
   <si>
     <t>VND-99812</t>
@@ -259,6 +212,18 @@
     <t>Selesai</t>
   </si>
   <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>Koordinasi dengan PLN area, listrik padam.</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>Listrik kembali normal, ATM online.</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:40 AM
 27-05-2026</t>
   </si>
@@ -281,59 +246,28 @@
     <t>Diebold</t>
   </si>
   <si>
-    <t xml:space="preserve">11:45
-12:30
-13:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>ATM out of service, cash handler error.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Vendor tiba di lokasi, penggantian part.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>ATM kembali beroperasi normal.</t>
-    </r>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>ATM out of service, cash handler error.</t>
   </si>
   <si>
     <t xml:space="preserve">01:20 PM
 27-05-2026</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>Vendor tiba di lokasi, penggantian part.</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>ATM kembali beroperasi normal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">02:10 PM
 27-05-2026</t>
   </si>
@@ -359,46 +293,27 @@
     <t>Lintasarta</t>
   </si>
   <si>
-    <t xml:space="preserve">14:12
-14:55
-15:00
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Jaringan kantor cabang down, eskalasi ke Lintasarta.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Lintasarta investigasi gangguan link.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+    <t>Jaringan kantor cabang down, eskalasi ke Lintasarta.</t>
+  </si>
+  <si>
+    <t>LA-55231</t>
+  </si>
+  <si>
+    <t>Dalam Proses</t>
+  </si>
+  <si>
+    <t>Monitoring Dilanjutkan oleh Shift berikutnya</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>Lintasarta investigasi gangguan link.</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -410,15 +325,6 @@
     </r>
   </si>
   <si>
-    <t>LA-55231</t>
-  </si>
-  <si>
-    <t>Dalam Proses</t>
-  </si>
-  <si>
-    <t>Monitoring Dilanjutkan oleh Shift berikutnya</t>
-  </si>
-  <si>
     <t xml:space="preserve">04:05 PM
 27-05-2026</t>
   </si>
@@ -435,131 +341,40 @@
     <t>Putus jalur fiber optik</t>
   </si>
   <si>
-    <t xml:space="preserve">16:10
-16:38
-17:00
-17:30
-18:45
-19:50
-20:15
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Menerima laporan jaringan kantor cabang Simpang Empat tidak dapat diakses, dilakukan pengecekan awal status link dan perangkat router di lokasi.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Konfirmasi ke vendor Lintasarta melalui WAG, vendor menginformasikan ada pekerjaan galian pihak ketiga yang memutus jalur fiber optik utama.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Eskalasi ke NOC vendor.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>TINDAK LANJUT MONITORING SELANJUTNYA</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Vendor menyampaikan estimasi penyambungan kembali jalur fiber optik paling cepat pukul 22:00 WIB, monitoring dilanjutkan berkala setiap 30 menit.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>Cek ulang status perangkat, jaringan masih down dan belum ada perubahan dari sisi vendor.</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="9"/>
-        <rFont val="Swis721 Lt BT"/>
-      </rPr>
-      <t>TINDAK LANJUT MONITORING SELANJUTNYA</t>
-    </r>
+    <t>Menerima laporan jaringan kantor cabang Simpang Empat tidak dapat diakses, dilakukan pengecekan awal status link dan perangkat router di lokasi.</t>
   </si>
   <si>
     <t>LA-55402</t>
+  </si>
+  <si>
+    <t>16:38</t>
+  </si>
+  <si>
+    <t>Konfirmasi ke vendor Lintasarta melalui WAG, vendor menginformasikan ada pekerjaan galian pihak ketiga yang memutus jalur fiber optik utama.</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Eskalasi ke NOC vendor.</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>Vendor menyampaikan estimasi penyambungan kembali jalur fiber optik paling cepat pukul 22:00 WIB, monitoring dilanjutkan berkala setiap 30 menit.</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>Cek ulang status perangkat, jaringan masih down dan belum ada perubahan dari sisi vendor.</t>
+  </si>
+  <si>
+    <t>20:15</t>
   </si>
   <si>
     <t>Padang, 27 Mei 2026</t>
@@ -648,7 +463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -671,11 +486,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -711,20 +563,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1118,7 +985,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S31"/>
+  <dimension ref="B1:S37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" width="2.86" customWidth="1"/>
@@ -1441,7 +1308,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" ht="78" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="13">
         <v>1</v>
       </c>
@@ -1469,282 +1336,570 @@
       <c r="J14" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="N14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="13" t="s">
+      <c r="O14" s="17">
+        <v>0.09722222221898846</v>
+      </c>
+      <c r="P14" s="18">
+        <v>140</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>44500</v>
+      </c>
+      <c r="R14" s="19">
+        <v>0.9968637992831542</v>
+      </c>
+      <c r="S14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="15">
-        <v>0.09722222221898846</v>
-      </c>
-      <c r="P14" s="16">
-        <v>140</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>44500</v>
-      </c>
-      <c r="R14" s="17">
-        <v>0.9968637992831542</v>
-      </c>
-      <c r="S14" s="14" t="s">
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="20" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" ht="78" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B15" s="13">
+      <c r="L15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="14"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="14"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" s="13">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="E17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="F17" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="N15" s="13" t="s">
+      <c r="J17" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="O15" s="15">
+      <c r="K17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="17">
         <v>0.06944444444525288</v>
       </c>
-      <c r="P15" s="16">
+      <c r="P17" s="18">
         <v>100</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="Q17" s="18">
         <v>44540</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R17" s="19">
         <v>0.9977598566308243</v>
       </c>
-      <c r="S15" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" ht="92" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B16" s="13">
+      <c r="S17" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="14"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="14"/>
+    </row>
+    <row r="20" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" s="13">
         <v>3</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J16" s="13" t="s">
+      <c r="C20" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="M16" s="13" t="s">
+      <c r="F20" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="G20" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13" t="s">
+      <c r="H20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R16" s="13"/>
-      <c r="S16" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" ht="330" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B17" s="13">
+      <c r="I20" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="R20" s="13"/>
+      <c r="S20" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="14"/>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" s="13">
         <v>4</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C23" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="J23" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="K23" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K17" s="13" t="s">
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="L17" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="R17" s="13"/>
-      <c r="S17" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C26" s="19" t="s">
+      <c r="R23" s="13"/>
+      <c r="S23" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="14"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="14"/>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="F26" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G26" s="19"/>
-      <c r="I26" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="J26" s="19"/>
-      <c r="O26" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="P26" s="19"/>
-      <c r="R26" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="S26" s="19"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-    </row>
-    <row r="31" ht="31" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C31" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="18"/>
-      <c r="F31" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" s="18"/>
-      <c r="I31" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="18"/>
-      <c r="O31" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="P31" s="18"/>
-      <c r="R31" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="S31" s="18"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="14"/>
+    </row>
+    <row r="27" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="14"/>
+    </row>
+    <row r="28" ht="48" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="14"/>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="14"/>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C32" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="24"/>
+      <c r="F32" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="24"/>
+      <c r="I32" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="J32" s="24"/>
+      <c r="O32" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="P32" s="24"/>
+      <c r="R32" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="S32" s="24"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="24"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+    </row>
+    <row r="37" ht="31" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C37" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="F37" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="23"/>
+      <c r="I37" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="J37" s="23"/>
+      <c r="O37" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="P37" s="23"/>
+      <c r="R37" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="S37" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="108">
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:R3"/>
     <mergeCell ref="G5:I5"/>
@@ -1784,21 +1939,75 @@
     <mergeCell ref="Q12:Q13"/>
     <mergeCell ref="R12:R13"/>
     <mergeCell ref="S12:S13"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="B25:S25"/>
-    <mergeCell ref="C26:D28"/>
-    <mergeCell ref="F26:G28"/>
-    <mergeCell ref="I26:J28"/>
-    <mergeCell ref="O26:P28"/>
-    <mergeCell ref="R26:S28"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="O14:O16"/>
+    <mergeCell ref="P14:P16"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="M17:M19"/>
+    <mergeCell ref="N17:N19"/>
+    <mergeCell ref="O17:O19"/>
+    <mergeCell ref="P17:P19"/>
+    <mergeCell ref="Q17:Q19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="N20:P22"/>
+    <mergeCell ref="Q20:R22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="M20:M22"/>
+    <mergeCell ref="S20:S22"/>
+    <mergeCell ref="N23:P29"/>
+    <mergeCell ref="Q23:R29"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="C23:C29"/>
+    <mergeCell ref="D23:D29"/>
+    <mergeCell ref="E23:E29"/>
+    <mergeCell ref="F23:F29"/>
+    <mergeCell ref="G23:G29"/>
+    <mergeCell ref="H23:H29"/>
+    <mergeCell ref="I23:I29"/>
+    <mergeCell ref="J23:J29"/>
+    <mergeCell ref="M23:M29"/>
+    <mergeCell ref="S23:S29"/>
+    <mergeCell ref="B31:S31"/>
+    <mergeCell ref="C32:D34"/>
+    <mergeCell ref="F32:G34"/>
+    <mergeCell ref="I32:J34"/>
+    <mergeCell ref="O32:P34"/>
+    <mergeCell ref="R32:S34"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="R37:S37"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
